--- a/Assets/@Resources/Data/Excel/BalanceConfig.xlsx
+++ b/Assets/@Resources/Data/Excel/BalanceConfig.xlsx
@@ -714,7 +714,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BOSS_REPEAT_GOLD_KILLS</t>
+          <t>BOSS_REWARD_KILLS</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -722,7 +722,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>재돌파 골드 = 처치 골드 × 이 값</t>
+          <t>보스 처치 보상 = 일반 처치 N마리 몫의 경험치·골드(매번). 첫 돌파는 크리스탈을 더 준다</t>
         </is>
       </c>
     </row>

--- a/Assets/@Resources/Data/Excel/BalanceConfig.xlsx
+++ b/Assets/@Resources/Data/Excel/BalanceConfig.xlsx
@@ -628,11 +628,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>보스 공격 배수</t>
+          <t>보스 공격 = 노드 평균 × 이 값. 1.5 는 새 캐릭터가 1-1 첫 보스에 쓰러졌다(벽은 죽음이 아니라 30초 제한이어야 한다)</t>
         </is>
       </c>
     </row>

--- a/Assets/@Resources/Data/Excel/BalanceConfig.xlsx
+++ b/Assets/@Resources/Data/Excel/BalanceConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -846,6 +846,216 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>HOTTIME_MINUTES</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>30</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>핫타임 한 번의 길이(분, 실제 시간)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>HOTTIME_ADS_PER_DAY</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>핫타임 종류별 광고로 켤 수 있는 하루 횟수</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>HOTTIME_CRYSTAL_COST</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>50</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>핫타임을 크리스탈로 켤 때 값</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>HOT_GOLD_MULT</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>골드 핫타임: 처치·방치 골드 배수</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>HOT_EXP_MULT</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>경험치 핫타임: 처치·방치 경험치 배수</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>HOT_ATK_PCT</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>20</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>전투 핫타임: 공격력 +%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>FREE_CRYSTAL_AD</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>30</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>광고 무료 크리스탈 양</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>FREE_CRYSTAL_ADS_PER_DAY</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>무료 크리스탈 광고 하루 횟수</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>MANDRAKE_CRYSTAL_COST</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>50</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>만드라고라 1개 값(크리스탈)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>OFFLINE_AD_MULT</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>오프라인 보상 광고 배수(받은 만큼 한 번 더 = 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>MONTHLY_DAYS</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>30</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>월정액 기간(일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>MONTHLY_DAILY_CRYSTAL</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>100</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>월정액 매일 받는 크리스탈</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>MONTHLY_OFFLINE_BONUS_HOURS</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>월정액 중 오프라인 정산 상한 추가 시간</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CRYSTAL_FIRST_BUY_MULT</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>크리스탈 상품 종류별 첫 구매 배수</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/BalanceConfig.xlsx
+++ b/Assets/@Resources/Data/Excel/BalanceConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1056,6 +1056,36 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TAP_ATTACK_INTERVAL</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>탭 공격 최소 간격(초, 공격속도 100% 기준 — 공속이 오르면 줄어든다). 자동 전투 주기는 AtkCooldown 1초</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TAP_INPUT_BUFFER</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>베는 중에 누른 입력을 기억하는 시간(초) — 끝나는 즉시 이어 벤다</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/BalanceConfig.xlsx
+++ b/Assets/@Resources/Data/Excel/BalanceConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1086,6 +1086,156 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>DUNGEON_TIME</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>60</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>요일 던전 제한 시간(초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>DUNGEON_FREE_PER_DAY</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>요일 던전 종류별 하루 무료 입장</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>DUNGEON_ADS_PER_DAY</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>요일 던전 종류별 하루 광고 입장</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DUNGEON_CRYSTAL_COST</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>30</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>요일 던전 크리스탈 입장 값(횟수 제한 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DUNGEON_GOLD_MULT</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>10</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>골드 던전: 처치당 보너스 = 그 스테이지 평균 골드 × 이 값(보통 처치 보상은 따로)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>DUNGEON_EXP_MULT</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>10</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>경험치 던전: 처치당 보너스 = 그 스테이지 평균 경험치 × 이 값</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>DUNGEON_MAT_MULT</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>3</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>재료 던전: 잡은 몬스터의 재료 드롭 × 이 값(확정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>DUNGEON_MANDRAKE_KILLS</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>20</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>재료 던전: 이 수만큼 잡을 때마다 만드라고라 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>DUNGEON_TODAY_MULT</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>오늘의 던전(요일마다 한 종류) 보상 배수</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>DUNGEON_SPAWN_DELAY</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>던전에서 몬스터가 쓰러진 뒤 다음이 나오기까지(초)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/BalanceConfig.xlsx
+++ b/Assets/@Resources/Data/Excel/BalanceConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1236,6 +1236,201 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>RELIC_COST_ONE</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>30</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>유물 1회 소환 크리스탈</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>RELIC_COST_TEN</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>270</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>유물 10회 소환 크리스탈(10% 할인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>RELIC_ADS_PER_DAY</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>유물 광고 소환 하루 횟수(1회 소환)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>RELIC_PITY</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>150</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>전설 천장 — 전설 없이 이 수 −1 번을 뽑으면 다음은 전설 확정</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>RELIC_MAX_LEVEL</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>10</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>유물 최대 레벨 — 넘치는 중복은 크리스탈 환급</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>RELIC_RATE_COMMON</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>70</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>일반 등급 확률(%) — 화면에 그대로 공개된다</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>RELIC_RATE_RARE</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>24</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>희귀 등급 확률(%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>RELIC_RATE_EPIC</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>영웅 등급 확률(%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>RELIC_RATE_LEGENDARY</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>전설 등급 확률(%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>RELIC_REFUND_COMMON</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>2</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>최대 레벨 일반 유물 중복 환급 크리스탈</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>RELIC_REFUND_RARE</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>5</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>최대 레벨 희귀 유물 중복 환급 크리스탈</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>RELIC_REFUND_EPIC</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>15</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>최대 레벨 영웅 유물 중복 환급 크리스탈</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>RELIC_REFUND_LEGENDARY</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>50</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>최대 레벨 전설 유물 중복 환급 크리스탈</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/BalanceConfig.xlsx
+++ b/Assets/@Resources/Data/Excel/BalanceConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1431,6 +1431,246 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>BOND_POINTS_PER_LEVEL</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>20</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>마을 사람 호감도 한 단계 = 이 점수</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>BOND_MAX_LEVEL</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>10</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>호감도 최대 단계</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>BOND_REQUESTS_PER_DAY</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>3</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>하루 배달 의뢰 수(현지 00시에 새로)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BOND_REQUEST_AFFECTION</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>10</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>의뢰를 끝내면 그 사람 호감도 +</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>BOND_REQUEST_CRYSTAL</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>10</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>크리스탈이 붙은 의뢰의 크리스탈</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>BOND_REQUEST_CRYSTAL_CHANCE</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>의뢰에 크리스탈이 붙을 확률</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>BOND_DELIVER_GOLD_PER_ITEM</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>3</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>재료 배달 골드 = 지역 평균 골드 × 개수 × 이 값</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>BOND_HUNT_GOLD_PER_KILL</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>2</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>소포 전달 골드 = 지역 평균 골드 × 마리 × 이 값</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>BOND_GIFTS_PER_DAY</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>3</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>사람마다 하루 선물 횟수</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>BOND_GIFT_ITEMS</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>5</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>선물 한 번 = 가장 많은 재료 이 개수</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>BOND_GIFT_AFFECTION</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>2</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>선물 한 번 호감도 +</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>BOND_PERK_RECEPTIONIST</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>10</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>접수원 호감도 단계당 의뢰 보상 +%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>BOND_PERK_ALCHEMIST</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>3</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>연금술사 호감도 단계당 회복력 +%</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>BOND_PERK_BLACKSMITH</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>3</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>대장장이 호감도 단계당 강화 비용 -%</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>BOND_PERK_PRIEST</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>10</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>수도원 사제 호감도 단계당 처치 숙련도 +1 확률 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>BOND_PERK_SHOPKEEPER</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>2</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>상점 주인 호감도 단계당 마을 상점 가격 -%</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/BalanceConfig.xlsx
+++ b/Assets/@Resources/Data/Excel/BalanceConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C83"/>
+  <dimension ref="A1:C98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1671,6 +1671,231 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>PROMO_MAX_TIER</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>10</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>시련 최대 단계</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PROMO_LEVEL_STEP</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>30</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>시련 N단계 도전 레벨 = 이 값 × N</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>PROMO_ATK_MULT</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>시련 단계당 공격력 배수(단계만큼 거듭제곱)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>PROMO_HP_MULT</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>시련 단계당 최대 체력 배수(단계만큼 거듭제곱)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>PROMO_BOSS_MULT</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>시험관 = 사냥하던 스테이지 보스 능력치 × 이 값</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>PROMO_TIME_LIMIT</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>45</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>시련 제한 시간(초, 맞붙은 뒤부터)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>PROMO_CRYSTAL</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>50</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>시련 통과 크리스탈 = 이 값 × 새 단계</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ABYSS_START_MULT</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>심연 1층 = 마지막 스테이지 몬스터 × 이 값</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>ABYSS_FLOOR_MULT</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>심연 한 층마다 능력치·보상 배수</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ABYSS_KILLS_PER_FLOOR</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>5</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>심연 보통 층 처치 수</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>ABYSS_BOSS_EVERY</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>10</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>심연 보스 층 간격</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>ABYSS_BOSS_MULT</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>심연 보스 = 마지막 스테이지 보스 × 층 배수 × 이 값</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>ABYSS_BOSS_TIME</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>30</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>심연 보스 제한 시간(초)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ABYSS_CRYSTAL_PER_FLOOR</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>5</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>심연 처음 넘긴 층마다 크리스탈</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>ABYSS_BOSS_CRYSTAL_MULT</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>5</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>심연 보스 층 크리스탈 배수</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/BalanceConfig.xlsx
+++ b/Assets/@Resources/Data/Excel/BalanceConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C98"/>
+  <dimension ref="A1:C101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1896,6 +1896,51 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>OFFDUTY_SIDE_REWARD_MULT</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>비번 일정이 채집·마을 일일 때 오프라인 골드·경험치 배수</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>OFFDUTY_GATHER_PER_KILL</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>채집: 오프라인 처치 1마리당 재료 수(그 지역 드롭 재료, 출현 가중)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>OFFDUTY_HELP_POINTS_PER_HOUR</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>마을 일: 오프라인 1시간당 마을 사람 모두의 호감도</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/BalanceConfig.xlsx
+++ b/Assets/@Resources/Data/Excel/BalanceConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1941,6 +1941,111 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>BOND_SCENE_LEVEL_1</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>3</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>마을 사람 이야기 1 이 열리는 호감도 단계</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>BOND_SCENE_LEVEL_2</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>6</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>이야기 2 가 열리는 호감도 단계</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>BOND_SCENE_LEVEL_3</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>10</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>이야기 3 이 열리는 호감도 단계</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>BOND_SCENE_CRYSTAL_1</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>30</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>이야기 1 을 다 보면 크리스탈</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>BOND_SCENE_CRYSTAL_2</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>60</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>이야기 2 를 다 보면 크리스탈</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>BOND_SCENE_CRYSTAL_3</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>150</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>이야기 3 을 다 보면 크리스탈</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>BOND_GIFT_LIKED_MULT</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>2</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>좋아하는 재료를 선물하면 호감도 배수</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/@Resources/Data/Excel/BalanceConfig.xlsx
+++ b/Assets/@Resources/Data/Excel/BalanceConfig.xlsx
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>270</v>
+        <v>900</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
